--- a/data/trans_orig/P34A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P34A_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre / solo 2023 en 2023</t>
+          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79251</t>
+          <t>76411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>138342</t>
+          <t>138437</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17851</t>
+          <t>17584</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40932</t>
+          <t>42369</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102423</t>
+          <t>104648</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>171003</t>
+          <t>168575</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95855</t>
+          <t>94802</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159441</t>
+          <t>157633</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29279</t>
+          <t>30092</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61057</t>
+          <t>64420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>134429</t>
+          <t>136917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>207633</t>
+          <t>208758</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83721</t>
+          <t>83329</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>143503</t>
+          <t>143067</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>103677</t>
+          <t>103187</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>148605</t>
+          <t>149068</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>200976</t>
+          <t>197790</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>276525</t>
+          <t>281015</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52430</t>
+          <t>52721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36946</t>
+          <t>37298</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73625</t>
+          <t>75348</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52918</t>
+          <t>52159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109039</t>
+          <t>106352</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21502</t>
+          <t>20603</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57985</t>
+          <t>64414</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44743</t>
+          <t>44512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84047</t>
+          <t>83517</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75322</t>
+          <t>74193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>132604</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68128</t>
+          <t>64530</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110391</t>
+          <t>105910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>25221</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60316</t>
+          <t>59847</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95294</t>
+          <t>93696</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>157693</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43686</t>
+          <t>44113</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83203</t>
+          <t>79191</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28277</t>
+          <t>28987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65992</t>
+          <t>66815</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80803</t>
+          <t>80012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>137761</t>
+          <t>136053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102811</t>
+          <t>104317</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>149316</t>
+          <t>149898</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>206132</t>
+          <t>206012</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>360640</t>
+          <t>360728</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>324064</t>
+          <t>324853</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>515860</t>
+          <t>524702</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>56,19%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63132</t>
+          <t>63990</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102872</t>
+          <t>104089</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>40625</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84542</t>
+          <t>85436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109574</t>
+          <t>112177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177616</t>
+          <t>177547</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50678</t>
+          <t>49672</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89058</t>
+          <t>90852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61613</t>
+          <t>59168</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124007</t>
+          <t>124994</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128130</t>
+          <t>125976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>201132</t>
+          <t>198493</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61099</t>
+          <t>59500</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>95793</t>
+          <t>94209</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35120</t>
+          <t>34509</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57162</t>
+          <t>56584</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101634</t>
+          <t>104144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142294</t>
+          <t>143765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71148</t>
+          <t>73007</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108261</t>
+          <t>108627</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26079</t>
+          <t>26939</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44404</t>
+          <t>45034</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104276</t>
+          <t>105498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146267</t>
+          <t>147104</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161448</t>
+          <t>161029</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>207032</t>
+          <t>207407</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>231503</t>
+          <t>231327</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>269984</t>
+          <t>271261</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>403565</t>
+          <t>405468</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>465509</t>
+          <t>464024</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63918</t>
+          <t>65170</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99726</t>
+          <t>99711</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66781</t>
+          <t>67545</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94797</t>
+          <t>96498</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139311</t>
+          <t>141118</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>184678</t>
+          <t>187962</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83779</t>
+          <t>84920</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120882</t>
+          <t>121899</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113818</t>
+          <t>112469</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>146066</t>
+          <t>146175</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>207009</t>
+          <t>209429</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>257521</t>
+          <t>258575</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27416</t>
+          <t>28328</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>101747</t>
+          <t>105682</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40183</t>
+          <t>39459</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62915</t>
+          <t>62919</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>76293</t>
+          <t>73198</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>153862</t>
+          <t>151394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30961</t>
+          <t>30845</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>112748</t>
+          <t>111349</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>32830</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>54148</t>
+          <t>53770</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>70893</t>
+          <t>69041</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>149423</t>
+          <t>149300</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>363269</t>
+          <t>363312</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>731367</t>
+          <t>714722</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>284249</t>
+          <t>294374</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>369016</t>
+          <t>372768</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>713127</t>
+          <t>711399</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1168744</t>
+          <t>1167360</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,01%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>52808</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>179591</t>
+          <t>177099</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>110320</t>
+          <t>108773</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>249004</t>
+          <t>222978</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>158140</t>
+          <t>161561</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>347156</t>
+          <t>344881</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>49145</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>151160</t>
+          <t>152155</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110597</t>
+          <t>109482</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>150087</t>
+          <t>150159</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>136076</t>
+          <t>137358</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>286578</t>
+          <t>288994</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>23208</t>
+          <t>22433</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42610</t>
+          <t>43413</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33622</t>
+          <t>32188</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>51122</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>59647</t>
+          <t>61096</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>88770</t>
+          <t>88722</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>28618</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>52264</t>
+          <t>52031</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16459</t>
+          <t>15889</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>31319</t>
+          <t>30297</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48485</t>
+          <t>49770</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>75519</t>
+          <t>76684</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>247727</t>
+          <t>247553</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>292111</t>
+          <t>292003</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>259061</t>
+          <t>257346</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>292327</t>
+          <t>292264</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>514761</t>
+          <t>516926</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>572538</t>
+          <t>570485</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>110941</t>
+          <t>112193</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>150228</t>
+          <t>150775</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>115271</t>
+          <t>113895</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>144174</t>
+          <t>144263</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>238779</t>
+          <t>238896</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>286213</t>
+          <t>286691</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>72253</t>
+          <t>73173</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>104561</t>
+          <t>105060</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>62951</t>
+          <t>64574</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>86902</t>
+          <t>88503</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>143537</t>
+          <t>145347</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>185060</t>
+          <t>185409</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14008</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>28652</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>35766</t>
+          <t>35209</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>18525</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>56912</t>
+          <t>56151</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>24739</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>29790</t>
+          <t>30759</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>16842</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>48467</t>
+          <t>48252</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>199364</t>
+          <t>200298</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>230249</t>
+          <t>230788</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>317209</t>
+          <t>317059</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>529446</t>
+          <t>530537</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>537933</t>
+          <t>538200</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>824912</t>
+          <t>803403</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>70057</t>
+          <t>70661</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>95416</t>
+          <t>95453</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>41663</t>
+          <t>42211</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>159101</t>
+          <t>159361</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>81717</t>
+          <t>96467</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>237649</t>
+          <t>239555</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>24507</t>
+          <t>24485</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>41989</t>
+          <t>42089</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>20164</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>76455</t>
+          <t>75673</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>38221</t>
+          <t>39832</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>108200</t>
+          <t>106475</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>16249</t>
+          <t>16047</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>27351</t>
+          <t>26956</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>14354</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>11081</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>22632</t>
+          <t>21671</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>133239</t>
+          <t>132003</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>157581</t>
+          <t>160014</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>127791</t>
+          <t>127343</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>153416</t>
+          <t>153586</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>266429</t>
+          <t>266284</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>305478</t>
+          <t>304733</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>75086</t>
+          <t>73129</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>98335</t>
+          <t>98118</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>169312</t>
+          <t>170001</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>199700</t>
+          <t>199240</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>250364</t>
+          <t>251818</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>289527</t>
+          <t>288823</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,95%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>23063</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>39659</t>
+          <t>40509</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>72698</t>
+          <t>73442</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>95406</t>
+          <t>96317</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>102108</t>
+          <t>102020</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>130913</t>
+          <t>129799</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>318403</t>
+          <t>310738</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>462396</t>
+          <t>457426</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>194492</t>
+          <t>193306</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>271469</t>
+          <t>270362</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>551010</t>
+          <t>551412</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>713080</t>
+          <t>712681</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>330344</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>474290</t>
+          <t>473739</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>177890</t>
+          <t>171489</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>249846</t>
+          <t>248403</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>546604</t>
+          <t>545513</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>706277</t>
+          <t>700575</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1403834</t>
+          <t>1400195</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2001886</t>
+          <t>2024877</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1672264</t>
+          <t>1674126</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2170552</t>
+          <t>2161076</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3116160</t>
+          <t>3120845</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3872411</t>
+          <t>3834732</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>471932</t>
+          <t>467717</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>674553</t>
+          <t>670081</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>620377</t>
+          <t>614433</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>843105</t>
+          <t>846267</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1185873</t>
+          <t>1199204</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1485947</t>
+          <t>1484528</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>366725</t>
+          <t>364188</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>520105</t>
+          <t>521798</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>514108</t>
+          <t>516866</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>689909</t>
+          <t>689143</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>949168</t>
+          <t>946127</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1187350</t>
+          <t>1183007</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34A_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P34A_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>105955</t>
+          <t>106681</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>76411</t>
+          <t>80615</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>138437</t>
+          <t>134416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28353</t>
+          <t>33942</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17584</t>
+          <t>21063</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42369</t>
+          <t>49230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>134308</t>
+          <t>140624</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104648</t>
+          <t>109031</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168575</t>
+          <t>172128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>125866</t>
+          <t>127961</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94802</t>
+          <t>98609</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>157633</t>
+          <t>157033</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>43882</t>
+          <t>45753</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30092</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64420</t>
+          <t>64519</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>169748</t>
+          <t>173714</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>136917</t>
+          <t>141636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>208758</t>
+          <t>214142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>110403</t>
+          <t>116551</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83329</t>
+          <t>88368</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>143067</t>
+          <t>148438</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>125893</t>
+          <t>150437</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>103187</t>
+          <t>125914</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>149068</t>
+          <t>176197</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236296</t>
+          <t>266988</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>197790</t>
+          <t>227403</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>281015</t>
+          <t>307611</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>18941</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7927</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52721</t>
+          <t>42848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53402</t>
+          <t>65867</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37298</t>
+          <t>46625</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75348</t>
+          <t>87691</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>73818</t>
+          <t>84808</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52159</t>
+          <t>59800</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106352</t>
+          <t>114952</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>37347</t>
+          <t>37658</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20603</t>
+          <t>22907</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64414</t>
+          <t>59291</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>61670</t>
+          <t>66512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44512</t>
+          <t>48165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83517</t>
+          <t>90163</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>99017</t>
+          <t>104170</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74193</t>
+          <t>78723</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>132604</t>
+          <t>136390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85709</t>
+          <t>91912</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64530</t>
+          <t>70159</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105910</t>
+          <t>115015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42706</t>
+          <t>44046</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25221</t>
+          <t>31260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59847</t>
+          <t>59246</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>128415</t>
+          <t>135958</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93696</t>
+          <t>110430</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157693</t>
+          <t>166703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>60829</t>
+          <t>69907</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44113</t>
+          <t>51612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79191</t>
+          <t>92580</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48076</t>
+          <t>49546</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28987</t>
+          <t>36045</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66815</t>
+          <t>66352</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>108904</t>
+          <t>119453</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>80012</t>
+          <t>97974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136053</t>
+          <t>146273</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>126262</t>
+          <t>154949</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104317</t>
+          <t>127146</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>149898</t>
+          <t>181935</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>254920</t>
+          <t>216863</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>206012</t>
+          <t>192532</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>360728</t>
+          <t>238314</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>381182</t>
+          <t>371812</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>324853</t>
+          <t>335347</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>524702</t>
+          <t>406338</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>82130</t>
+          <t>82891</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63990</t>
+          <t>64265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104089</t>
+          <t>109465</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>72763</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40625</t>
+          <t>57964</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85436</t>
+          <t>90886</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>147394</t>
+          <t>155654</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112177</t>
+          <t>130058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177547</t>
+          <t>185457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>67432</t>
+          <t>75926</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49672</t>
+          <t>58114</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90852</t>
+          <t>98938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>100538</t>
+          <t>117865</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59168</t>
+          <t>98478</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124994</t>
+          <t>136589</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>167970</t>
+          <t>193792</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125976</t>
+          <t>164834</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>198493</t>
+          <t>222976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>422361</t>
+          <t>475585</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>422361</t>
+          <t>475585</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>422361</t>
+          <t>475585</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>933865</t>
+          <t>976669</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>933865</t>
+          <t>976669</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>933865</t>
+          <t>976669</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>77018</t>
+          <t>83308</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59500</t>
+          <t>66432</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94209</t>
+          <t>104928</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>45196</t>
+          <t>48868</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34509</t>
+          <t>38175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56584</t>
+          <t>60800</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>122214</t>
+          <t>132176</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104144</t>
+          <t>112515</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143765</t>
+          <t>155229</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>88490</t>
+          <t>95729</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73007</t>
+          <t>79583</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108627</t>
+          <t>117825</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>35039</t>
+          <t>38889</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26939</t>
+          <t>29628</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45034</t>
+          <t>50195</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>123529</t>
+          <t>134618</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105498</t>
+          <t>114272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>147104</t>
+          <t>157528</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>184757</t>
+          <t>219913</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161029</t>
+          <t>195407</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>207407</t>
+          <t>243848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>250156</t>
+          <t>286394</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>231327</t>
+          <t>266629</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>271261</t>
+          <t>308661</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>434913</t>
+          <t>506306</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>405468</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>464024</t>
+          <t>541411</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>80657</t>
+          <t>88550</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65170</t>
+          <t>71736</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>99711</t>
+          <t>110197</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>80590</t>
+          <t>93932</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67545</t>
+          <t>77559</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96498</t>
+          <t>108612</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>161247</t>
+          <t>182482</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>141118</t>
+          <t>157636</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>187962</t>
+          <t>206749</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>102879</t>
+          <t>130773</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84920</t>
+          <t>110237</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121899</t>
+          <t>152708</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>129884</t>
+          <t>151784</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>112469</t>
+          <t>133529</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>146175</t>
+          <t>170676</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>232763</t>
+          <t>282557</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>209429</t>
+          <t>254714</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258575</t>
+          <t>315110</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>533801</t>
+          <t>618273</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>533801</t>
+          <t>618273</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>533801</t>
+          <t>618273</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>540865</t>
+          <t>619868</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>540865</t>
+          <t>619868</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>540865</t>
+          <t>619868</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1074666</t>
+          <t>1238140</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1074666</t>
+          <t>1238140</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1074666</t>
+          <t>1238140</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>70419</t>
+          <t>76589</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28328</t>
+          <t>61068</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105682</t>
+          <t>95546</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50717</t>
+          <t>54662</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39459</t>
+          <t>44125</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62919</t>
+          <t>67449</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>121135</t>
+          <t>131251</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73198</t>
+          <t>112682</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>151394</t>
+          <t>151315</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>75173</t>
+          <t>78294</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30845</t>
+          <t>62860</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>111349</t>
+          <t>98744</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>42930</t>
+          <t>47124</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32830</t>
+          <t>37722</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53770</t>
+          <t>58989</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>118103</t>
+          <t>125419</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>69041</t>
+          <t>107307</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>149300</t>
+          <t>150064</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>516793</t>
+          <t>295688</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>363312</t>
+          <t>272334</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>714722</t>
+          <t>323364</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>343970</t>
+          <t>376005</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>294374</t>
+          <t>352738</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>372768</t>
+          <t>396813</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>860762</t>
+          <t>671694</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>711399</t>
+          <t>640422</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1167360</t>
+          <t>707569</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>49,29%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>120878</t>
+          <t>131841</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>111999</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177099</t>
+          <t>154757</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>142276</t>
+          <t>117744</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>108773</t>
+          <t>104027</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>222978</t>
+          <t>135728</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>263154</t>
+          <t>249585</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>161561</t>
+          <t>223012</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>344881</t>
+          <t>275241</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>103474</t>
+          <t>117075</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>49145</t>
+          <t>99177</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>152155</t>
+          <t>138729</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>132230</t>
+          <t>140572</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>109482</t>
+          <t>125470</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>150159</t>
+          <t>159049</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>235704</t>
+          <t>257647</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>137358</t>
+          <t>233672</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>288994</t>
+          <t>284348</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>886737</t>
+          <t>699488</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>886737</t>
+          <t>699488</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>886737</t>
+          <t>699488</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>712122</t>
+          <t>736107</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>712122</t>
+          <t>736107</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>712122</t>
+          <t>736107</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1598858</t>
+          <t>1435596</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1598858</t>
+          <t>1435596</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1598858</t>
+          <t>1435596</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>31924</t>
+          <t>35320</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22433</t>
+          <t>25507</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>43413</t>
+          <t>48980</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>41459</t>
+          <t>46037</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>32188</t>
+          <t>36812</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51122</t>
+          <t>57986</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>73383</t>
+          <t>81357</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>61096</t>
+          <t>67552</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>88722</t>
+          <t>96725</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>39317</t>
+          <t>45935</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28618</t>
+          <t>34112</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>52031</t>
+          <t>59410</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>22489</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>18136</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30297</t>
+          <t>33889</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>61806</t>
+          <t>70670</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49770</t>
+          <t>57422</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>76684</t>
+          <t>85876</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>268290</t>
+          <t>286251</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>247553</t>
+          <t>260767</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>292003</t>
+          <t>310804</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>274882</t>
+          <t>307871</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>257346</t>
+          <t>287715</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>292264</t>
+          <t>327140</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>543172</t>
+          <t>594122</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>516926</t>
+          <t>565574</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>570485</t>
+          <t>624670</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>131706</t>
+          <t>141888</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>112193</t>
+          <t>123143</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>150775</t>
+          <t>166799</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>129540</t>
+          <t>144936</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>113895</t>
+          <t>128811</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>144263</t>
+          <t>162137</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>261247</t>
+          <t>286824</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>238896</t>
+          <t>261260</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>313248</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>88047</t>
+          <t>98059</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>73173</t>
+          <t>81709</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>105060</t>
+          <t>115888</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>75131</t>
+          <t>81715</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>64574</t>
+          <t>70095</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>88503</t>
+          <t>95561</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>163178</t>
+          <t>179774</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>145347</t>
+          <t>157658</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>185409</t>
+          <t>201569</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>559284</t>
+          <t>607453</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>559284</t>
+          <t>607453</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>559284</t>
+          <t>607453</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>543501</t>
+          <t>605294</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>543501</t>
+          <t>605294</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>543501</t>
+          <t>605294</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1102785</t>
+          <t>1212747</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1102785</t>
+          <t>1212747</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1102785</t>
+          <t>1212747</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>20315</t>
+          <t>22199</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14116</t>
+          <t>15741</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>29088</t>
+          <t>31243</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>21068</t>
+          <t>23492</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>16585</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>35209</t>
+          <t>31312</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>41383</t>
+          <t>45691</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>35637</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>56151</t>
+          <t>56538</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>16508</t>
+          <t>18711</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11385</t>
+          <t>12365</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24739</t>
+          <t>27098</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>17969</t>
+          <t>20336</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>14796</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>30759</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>34476</t>
+          <t>39047</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16842</t>
+          <t>30949</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>48252</t>
+          <t>49984</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>215910</t>
+          <t>237646</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>200298</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>230788</t>
+          <t>252508</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>419895</t>
+          <t>231294</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>317059</t>
+          <t>215261</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>530537</t>
+          <t>246092</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>635805</t>
+          <t>468940</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>538200</t>
+          <t>447006</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>803403</t>
+          <t>491011</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>58,14%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>81883</t>
+          <t>92580</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>70661</t>
+          <t>77195</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>95453</t>
+          <t>106794</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>101227</t>
+          <t>112495</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>42211</t>
+          <t>99574</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>159361</t>
+          <t>127846</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>183110</t>
+          <t>205075</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>96467</t>
+          <t>185432</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>239555</t>
+          <t>223789</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>32686</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>24485</t>
+          <t>26093</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>42089</t>
+          <t>45503</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>47631</t>
+          <t>50952</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>19669</t>
+          <t>41384</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>75673</t>
+          <t>61549</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>80316</t>
+          <t>85843</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>39832</t>
+          <t>73184</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>106475</t>
+          <t>101363</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>367301</t>
+          <t>406027</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>367301</t>
+          <t>406027</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>367301</t>
+          <t>406027</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438568</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438568</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>438568</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>975090</t>
+          <t>844595</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>975090</t>
+          <t>844595</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>975090</t>
+          <t>844595</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>18827</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>14559</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>19583</t>
+          <t>22267</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>16605</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>26956</t>
+          <t>30699</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>10634</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>17503</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,22 +4965,22 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>7234</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>10449</t>
+          <t>11663</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>21671</t>
+          <t>25204</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>145743</t>
+          <t>158404</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>132003</t>
+          <t>143378</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>160014</t>
+          <t>172527</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>140541</t>
+          <t>153311</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>127343</t>
+          <t>137267</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>153586</t>
+          <t>167253</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>286284</t>
+          <t>311716</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>266284</t>
+          <t>289955</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>304733</t>
+          <t>332099</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>85784</t>
+          <t>93985</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>73129</t>
+          <t>81437</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>98118</t>
+          <t>108527</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>183349</t>
+          <t>201889</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>170001</t>
+          <t>187925</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>199240</t>
+          <t>220976</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>269133</t>
+          <t>295874</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>251818</t>
+          <t>274981</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>288823</t>
+          <t>317519</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,19%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>30784</t>
+          <t>33246</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>25095</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>40509</t>
+          <t>42042</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>84280</t>
+          <t>89804</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>73442</t>
+          <t>77937</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>96317</t>
+          <t>104047</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>115064</t>
+          <t>123050</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>102020</t>
+          <t>109069</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>129799</t>
+          <t>140464</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>281075</t>
+          <t>308174</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>281075</t>
+          <t>308174</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>281075</t>
+          <t>308174</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>424269</t>
+          <t>462600</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>424269</t>
+          <t>462600</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>424269</t>
+          <t>462600</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>705343</t>
+          <t>770774</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>705343</t>
+          <t>770774</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>705343</t>
+          <t>770774</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>401516</t>
+          <t>427915</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>310738</t>
+          <t>385967</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>457426</t>
+          <t>476861</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,32 +5534,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>238907</t>
+          <t>261409</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>193306</t>
+          <t>233955</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>270362</t>
+          <t>289961</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>640422</t>
+          <t>689324</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>551412</t>
+          <t>638639</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>712681</t>
+          <t>746470</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>414771</t>
+          <t>447172</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>330344</t>
+          <t>401215</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>473739</t>
+          <t>498606</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>217074</t>
+          <t>233617</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>171489</t>
+          <t>207093</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>248403</t>
+          <t>262965</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>631845</t>
+          <t>680788</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>545513</t>
+          <t>627055</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>700575</t>
+          <t>742880</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1568158</t>
+          <t>1469402</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1400195</t>
+          <t>1406597</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2024877</t>
+          <t>1531002</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1810256</t>
+          <t>1722176</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1674126</t>
+          <t>1664885</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2161076</t>
+          <t>1772304</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>3378413</t>
+          <t>3191578</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3120845</t>
+          <t>3106798</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3834732</t>
+          <t>3273976</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>603454</t>
+          <t>650676</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>467717</t>
+          <t>604745</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>670081</t>
+          <t>705451</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>755648</t>
+          <t>809626</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>614433</t>
+          <t>766475</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>846267</t>
+          <t>857682</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>1359102</t>
+          <t>1460302</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1199204</t>
+          <t>1395217</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1484528</t>
+          <t>1529639</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>462648</t>
+          <t>527629</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>364188</t>
+          <t>482240</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>521798</t>
+          <t>573044</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>631364</t>
+          <t>699204</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>516866</t>
+          <t>660686</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>689143</t>
+          <t>742218</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>1094012</t>
+          <t>1226833</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>946127</t>
+          <t>1160389</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1183007</t>
+          <t>1289408</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
